--- a/metadata/plate_metadata/20260415_cep290_18hpf_plate03_well_metadata.xlsx
+++ b/metadata/plate_metadata/20260415_cep290_18hpf_plate03_well_metadata.xlsx
@@ -900,7 +900,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G2" s="8" t="n"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G3" s="8" t="n"/>
@@ -967,12 +967,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G4" s="8" t="n"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G7" s="8" t="n"/>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
